--- a/Perplexity_paket_Taganay_2024_2025/taganay_perplexity_2024_2025/Osv60_soc_taxi_2025.xlsx
+++ b/Perplexity_paket_Taganay_2024_2025/taganay_perplexity_2024_2025/Osv60_soc_taxi_2025.xlsx
@@ -1610,7 +1610,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:H6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1631,20 +1631,25 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>Внутренняя_группа</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>Оборот_Дт</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Оборот_Кт</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>База_для_расчёта</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Причина_исключения</t>
         </is>
@@ -1664,8 +1669,10 @@
           <t>такси</t>
         </is>
       </c>
-      <c r="D2" t="n">
-        <v>573525.4</v>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Ремонт и обслуживание автомобиля</t>
+        </is>
       </c>
       <c r="E2" t="n">
         <v>573525.4</v>
@@ -1673,7 +1680,10 @@
       <c r="F2" t="n">
         <v>573525.4</v>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="G2" t="n">
+        <v>573525.4</v>
+      </c>
+      <c r="H2" t="inlineStr">
         <is>
           <t>нет правила классификации для соцтакси</t>
         </is>
@@ -1693,8 +1703,10 @@
           <t>такси</t>
         </is>
       </c>
-      <c r="D3" t="n">
-        <v>408617</v>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Ремонт и обслуживание автомобиля</t>
+        </is>
       </c>
       <c r="E3" t="n">
         <v>408617</v>
@@ -1702,7 +1714,10 @@
       <c r="F3" t="n">
         <v>408617</v>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="G3" t="n">
+        <v>408617</v>
+      </c>
+      <c r="H3" t="inlineStr">
         <is>
           <t>нет правила классификации для соцтакси</t>
         </is>
@@ -1722,8 +1737,10 @@
           <t>такси</t>
         </is>
       </c>
-      <c r="D4" t="n">
-        <v>77000</v>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Связь, IT и офисные расходы</t>
+        </is>
       </c>
       <c r="E4" t="n">
         <v>77000</v>
@@ -1731,7 +1748,10 @@
       <c r="F4" t="n">
         <v>77000</v>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="G4" t="n">
+        <v>77000</v>
+      </c>
+      <c r="H4" t="inlineStr">
         <is>
           <t>нет правила классификации для соцтакси</t>
         </is>
@@ -1751,8 +1771,10 @@
           <t>такси</t>
         </is>
       </c>
-      <c r="D5" t="n">
-        <v>417674.82</v>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Ремонт и обслуживание автомобиля</t>
+        </is>
       </c>
       <c r="E5" t="n">
         <v>417674.82</v>
@@ -1760,7 +1782,10 @@
       <c r="F5" t="n">
         <v>417674.82</v>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="G5" t="n">
+        <v>417674.82</v>
+      </c>
+      <c r="H5" t="inlineStr">
         <is>
           <t>нет правила классификации для соцтакси</t>
         </is>
@@ -1780,8 +1805,10 @@
           <t>такси</t>
         </is>
       </c>
-      <c r="D6" t="n">
-        <v>240410.46</v>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Топливо (ГСМ)</t>
+        </is>
       </c>
       <c r="E6" t="n">
         <v>240410.46</v>
@@ -1789,7 +1816,10 @@
       <c r="F6" t="n">
         <v>240410.46</v>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="G6" t="n">
+        <v>240410.46</v>
+      </c>
+      <c r="H6" t="inlineStr">
         <is>
           <t>нет правила классификации для соцтакси</t>
         </is>
